--- a/data/trans_dic/IP42B-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP42B-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>La persona sustentadora principal recibe una pensión</t>
+          <t>La persona sustentadora principal recibe una pensión (tasa de respuesta: 28,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,87</t>
+          <t>0,0; 18,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,33; 25,57</t>
+          <t>7,32; 26,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,97</t>
+          <t>1,16; 10,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,67</t>
+          <t>0,0; 18,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 26,78</t>
+          <t>8,24; 28,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,07; 23,61</t>
+          <t>5,74; 22,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,86</t>
+          <t>0,0; 13,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 23,11</t>
+          <t>9,9; 23,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,14; 15,18</t>
+          <t>4,02; 14,05</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 11,44</t>
+          <t>1,36; 11,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,43; 26,97</t>
+          <t>11,04; 30,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 14,62</t>
+          <t>3,2; 14,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,61</t>
+          <t>1,15; 10,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,82; 23,07</t>
+          <t>9,09; 24,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 9,55</t>
+          <t>1,65; 9,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 8,89</t>
+          <t>1,93; 8,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,99; 23,27</t>
+          <t>11,51; 22,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 9,33</t>
+          <t>2,84; 9,4</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 35,04</t>
+          <t>4,39; 36,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 22,23</t>
+          <t>5,07; 22,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 16,2</t>
+          <t>3,59; 16,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,25; 33,08</t>
+          <t>9,23; 32,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,72; 26,19</t>
+          <t>6,53; 25,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 13,23</t>
+          <t>2,4; 12,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,27; 29,29</t>
+          <t>9,77; 28,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,08; 20,63</t>
+          <t>7,54; 20,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 11,57</t>
+          <t>3,81; 11,94</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 21,21</t>
+          <t>6,5; 21,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,37; 29,15</t>
+          <t>9,44; 28,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 24,04</t>
+          <t>6,94; 22,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 12,87</t>
+          <t>1,35; 12,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 19,47</t>
+          <t>3,58; 18,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,74; 17,31</t>
+          <t>4,75; 17,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 14,19</t>
+          <t>5,11; 13,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,49; 20,86</t>
+          <t>8,36; 20,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 17,97</t>
+          <t>7,12; 16,61</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 13,94</t>
+          <t>5,59; 13,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,54; 20,23</t>
+          <t>11,22; 20,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 12,02</t>
+          <t>5,65; 12,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 10,93</t>
+          <t>4,31; 11,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,09; 18,63</t>
+          <t>10,14; 18,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 10,64</t>
+          <t>5,11; 10,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,77</t>
+          <t>5,68; 10,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,98; 17,86</t>
+          <t>12,05; 18,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,96; 10,07</t>
+          <t>6,03; 10,32</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>La persona sustentadora principal recibe una pensión (tasa de respuesta: 28,99%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6632</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1643</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>6687</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4860</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>13319</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6502</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3254</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3202; 11440</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>462; 4349</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3525</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3416; 11820</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2222; 8788</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4873</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8430; 19965</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3155; 11025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9983</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4570</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>9804</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4660</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>19787</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7838</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>617; 5170</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6156; 16853</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1981; 8923</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>677; 6208</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5849; 15439</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1288; 7260</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2005; 9342</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>13822; 27325</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3981; 13154</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2983</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4003</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3831</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5670</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5939</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>8653</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>9941</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>7381</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>803; 6588</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1841; 8120</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1757; 8108</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2788; 9853</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2676; 10478</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1382; 7221</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4736; 13647</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5827; 15744</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4057; 12725</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6909</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7607</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6985</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2672</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3964</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9581</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>11571</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>12874</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3585; 11908</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4055; 12302</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3568; 11795</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>709; 6693</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1475; 7711</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2860; 10520</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5504; 15050</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>7035; 17567</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>7950; 18536</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>12496</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28224</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17029</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26394</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17567</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>24261</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>54618</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>34596</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>7602; 18744</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>20048; 36695</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11426; 24573</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6922; 17956</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>19076; 35275</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>11986; 24817</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16854; 32322</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>44175; 66638</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>26344; 45078</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP42B-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP42B-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,96</t>
+          <t>0,0; 18,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 26,17</t>
+          <t>7,62; 25,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,94</t>
+          <t>1,16; 11,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,2</t>
+          <t>0,0; 18,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,24; 28,5</t>
+          <t>7,8; 27,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,74; 22,71</t>
+          <t>5,69; 23,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,34</t>
+          <t>0,0; 13,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,9; 23,43</t>
+          <t>9,78; 23,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,02; 14,05</t>
+          <t>4,38; 14,85</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,39</t>
+          <t>1,36; 11,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,04; 30,24</t>
+          <t>10,38; 26,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 14,42</t>
+          <t>3,15; 14,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,58</t>
+          <t>1,18; 11,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,09; 24,0</t>
+          <t>9,13; 23,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 9,3</t>
+          <t>1,61; 9,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 8,98</t>
+          <t>1,88; 8,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,51; 22,76</t>
+          <t>11,03; 22,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,4</t>
+          <t>3,06; 9,47</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 36,05</t>
+          <t>4,63; 35,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,07; 22,36</t>
+          <t>5,06; 21,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 16,55</t>
+          <t>2,65; 16,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,23; 32,61</t>
+          <t>9,43; 33,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 25,58</t>
+          <t>6,57; 24,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 12,54</t>
+          <t>2,43; 13,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,77; 28,14</t>
+          <t>9,33; 28,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,54; 20,37</t>
+          <t>7,55; 20,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 11,94</t>
+          <t>3,72; 11,92</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 21,57</t>
+          <t>6,02; 19,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,44; 28,65</t>
+          <t>9,15; 29,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 22,93</t>
+          <t>6,85; 23,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 12,74</t>
+          <t>1,26; 11,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 18,69</t>
+          <t>3,89; 18,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 17,49</t>
+          <t>4,62; 17,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 13,97</t>
+          <t>4,95; 13,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,36; 20,87</t>
+          <t>8,06; 20,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 16,61</t>
+          <t>7,05; 17,66</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,59; 13,78</t>
+          <t>5,84; 13,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,22; 20,53</t>
+          <t>11,87; 20,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,65; 12,16</t>
+          <t>6,03; 12,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,31; 11,17</t>
+          <t>4,26; 10,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,14; 18,76</t>
+          <t>10,34; 18,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,11; 10,58</t>
+          <t>4,91; 10,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 10,89</t>
+          <t>5,84; 11,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,05; 18,17</t>
+          <t>11,94; 18,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 10,32</t>
+          <t>6,01; 10,41</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3254</t>
+          <t>0; 3219</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3202; 11440</t>
+          <t>3332; 11325</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>462; 4349</t>
+          <t>461; 4573</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3525</t>
+          <t>0; 3507</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3416; 11820</t>
+          <t>3237; 11322</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2222; 8788</t>
+          <t>2201; 9184</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4873</t>
+          <t>0; 4757</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8430; 19965</t>
+          <t>8335; 19924</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3155; 11025</t>
+          <t>3439; 11650</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>617; 5170</t>
+          <t>619; 5262</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6156; 16853</t>
+          <t>5785; 14811</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1981; 8923</t>
+          <t>1948; 9125</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>677; 6208</t>
+          <t>694; 6775</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5849; 15439</t>
+          <t>5872; 14830</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1288; 7260</t>
+          <t>1261; 7682</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2005; 9342</t>
+          <t>1958; 8707</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13822; 27325</t>
+          <t>13243; 26963</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3981; 13154</t>
+          <t>4288; 13255</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>803; 6588</t>
+          <t>847; 6495</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1841; 8120</t>
+          <t>1839; 7983</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1757; 8108</t>
+          <t>1296; 7844</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2788; 9853</t>
+          <t>2850; 10168</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2676; 10478</t>
+          <t>2690; 10194</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1382; 7221</t>
+          <t>1399; 7848</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4736; 13647</t>
+          <t>4522; 13958</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5827; 15744</t>
+          <t>5836; 15586</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4057; 12725</t>
+          <t>3961; 12702</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3585; 11908</t>
+          <t>3325; 10863</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4055; 12302</t>
+          <t>3926; 12529</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3568; 11795</t>
+          <t>3523; 11985</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>709; 6693</t>
+          <t>660; 6042</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1475; 7711</t>
+          <t>1604; 7755</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2860; 10520</t>
+          <t>2782; 10761</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5504; 15050</t>
+          <t>5330; 15042</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7035; 17567</t>
+          <t>6789; 17104</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7950; 18536</t>
+          <t>7870; 19710</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7602; 18744</t>
+          <t>7944; 18363</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20048; 36695</t>
+          <t>21221; 37511</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11426; 24573</t>
+          <t>12180; 24540</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6922; 17956</t>
+          <t>6845; 17396</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19076; 35275</t>
+          <t>19449; 35299</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11986; 24817</t>
+          <t>11510; 25294</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16854; 32322</t>
+          <t>17329; 33111</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>44175; 66638</t>
+          <t>43786; 66645</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26344; 45078</t>
+          <t>26230; 45458</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP42B-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP42B-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12,56%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,88%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>15,17%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,13%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,76</t>
+          <t>0,0; 18,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,62; 25,9</t>
+          <t>7,81; 26,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 11,5</t>
+          <t>5,07; 23,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,11</t>
+          <t>0,0; 19,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,8; 27,3</t>
+          <t>7,33; 25,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 23,73</t>
+          <t>1,18; 10,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,02</t>
+          <t>0,0; 12,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,78; 23,39</t>
+          <t>9,63; 23,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 14,85</t>
+          <t>4,14; 15,18</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15,24%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>4,27%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>17,91%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,39%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>15,24%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,59</t>
+          <t>1,16; 10,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,38; 26,57</t>
+          <t>8,82; 23,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 14,74</t>
+          <t>1,64; 9,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,54</t>
+          <t>1,35; 11,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,13; 23,05</t>
+          <t>10,43; 26,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 9,84</t>
+          <t>3,12; 14,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 8,37</t>
+          <t>2,0; 8,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,03; 22,45</t>
+          <t>10,99; 23,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 9,47</t>
+          <t>2,81; 9,33</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>18,77%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>16,32%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>11,02%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7,82%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 35,54</t>
+          <t>9,25; 33,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 21,98</t>
+          <t>7,72; 26,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 16,01</t>
+          <t>2,37; 13,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,43; 33,65</t>
+          <t>4,35; 35,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 24,89</t>
+          <t>3,81; 22,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 13,63</t>
+          <t>2,83; 16,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,33; 28,78</t>
+          <t>10,27; 29,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,55; 20,17</t>
+          <t>8,08; 20,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 11,92</t>
+          <t>3,56; 11,57</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,61%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,79%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>12,52%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>17,72%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13,58%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 19,68</t>
+          <t>1,36; 12,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,15; 29,18</t>
+          <t>4,38; 19,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 23,3</t>
+          <t>4,74; 17,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 11,51</t>
+          <t>6,09; 21,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 18,8</t>
+          <t>9,37; 29,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 17,89</t>
+          <t>7,35; 24,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 13,96</t>
+          <t>5,46; 14,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,06; 20,32</t>
+          <t>8,49; 20,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 17,66</t>
+          <t>7,07; 17,97</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>9,19%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>15,79%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>8,43%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,84; 13,5</t>
+          <t>4,37; 10,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,87; 20,99</t>
+          <t>10,09; 18,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 12,14</t>
+          <t>4,81; 10,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,82</t>
+          <t>5,52; 13,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,34; 18,77</t>
+          <t>11,54; 20,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 10,78</t>
+          <t>5,69; 12,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,84; 11,15</t>
+          <t>5,83; 10,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,94; 18,17</t>
+          <t>11,98; 17,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,01; 10,41</t>
+          <t>5,96; 10,07</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1316,27 +1316,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6687</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4860</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>665</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>6632</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1643</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>6687</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4860</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3219</t>
+          <t>0; 3617</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3332; 11325</t>
+          <t>3241; 11108</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>461; 4573</t>
+          <t>1964; 9137</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3507</t>
+          <t>0; 3410</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3237; 11322</t>
+          <t>3203; 11180</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2201; 9184</t>
+          <t>470; 4362</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4757</t>
+          <t>0; 4697</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8335; 19924</t>
+          <t>8203; 19686</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3439; 11650</t>
+          <t>3247; 11909</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9804</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1939</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>9983</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4570</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2721</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9804</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3268</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>619; 5262</t>
+          <t>683; 6226</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5785; 14811</t>
+          <t>5678; 14846</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1948; 9125</t>
+          <t>1282; 7460</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>694; 6775</t>
+          <t>612; 5196</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5872; 14830</t>
+          <t>5811; 15033</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1261; 7682</t>
+          <t>1932; 9049</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1958; 8707</t>
+          <t>2085; 9257</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13243; 26963</t>
+          <t>13194; 27937</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4288; 13255</t>
+          <t>3937; 13066</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5670</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5939</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>2983</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>4003</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3831</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5670</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5939</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3550</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>847; 6495</t>
+          <t>2794; 9997</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1839; 7983</t>
+          <t>3162; 10728</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1296; 7844</t>
+          <t>1365; 7617</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2850; 10168</t>
+          <t>796; 6405</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2690; 10194</t>
+          <t>1382; 8074</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1399; 7848</t>
+          <t>1387; 7938</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4522; 13958</t>
+          <t>4980; 14201</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5836; 15586</t>
+          <t>6247; 15942</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3961; 12702</t>
+          <t>3798; 12336</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2672</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3964</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>6909</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>7607</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6985</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2672</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3964</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5889</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3325; 10863</t>
+          <t>714; 6759</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3926; 12529</t>
+          <t>1808; 8030</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3523; 11985</t>
+          <t>2850; 10412</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>660; 6042</t>
+          <t>3360; 11709</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1604; 7755</t>
+          <t>4024; 12516</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2782; 10761</t>
+          <t>3782; 12363</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5330; 15042</t>
+          <t>5886; 15282</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6789; 17104</t>
+          <t>7151; 17560</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7870; 19710</t>
+          <t>7888; 20055</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>11764</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26394</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17567</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>12496</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>28224</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>17029</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>11764</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>26394</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>17567</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7944; 18363</t>
+          <t>7026; 17578</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21221; 37511</t>
+          <t>18970; 35036</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12180; 24540</t>
+          <t>11284; 24965</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6845; 17396</t>
+          <t>7509; 18963</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19449; 35299</t>
+          <t>20630; 36151</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11510; 25294</t>
+          <t>11500; 24287</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17329; 33111</t>
+          <t>17297; 31965</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>43786; 66645</t>
+          <t>43936; 65513</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26230; 45458</t>
+          <t>26016; 43951</t>
         </is>
       </c>
     </row>
